--- a/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
+++ b/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
@@ -99,7 +99,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20260330120000</t>
   </si>
   <si>
     <t/>

--- a/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
+++ b/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
@@ -99,7 +99,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20260330120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20240628120000</t>
   </si>
   <si>
     <t/>

--- a/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
+++ b/ig/DM-MARS-2026/ASS-X09-DepartementOM-RegionOM.xlsx
@@ -99,7 +99,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20260505120000</t>
   </si>
   <si>
     <t/>
